--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,64 +55,43 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>В5832ХЕ</t>
   </si>
   <si>
     <t>В6367ТА</t>
   </si>
   <si>
-    <t>В5832ХЕ</t>
+    <t>78970155027720352</t>
   </si>
   <si>
     <t>78970155027720378</t>
   </si>
   <si>
-    <t>78970155027720352</t>
-  </si>
-  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>06:25:00</t>
-  </si>
-  <si>
-    <t>09:59:00</t>
-  </si>
-  <si>
-    <t>06:10:00</t>
-  </si>
-  <si>
-    <t>09:46:00</t>
-  </si>
-  <si>
-    <t>05:07:00</t>
-  </si>
-  <si>
-    <t>04:57:00</t>
-  </si>
-  <si>
-    <t>3236528218 3236528218</t>
-  </si>
-  <si>
-    <t>3236555141 3236555141</t>
-  </si>
-  <si>
-    <t>3236848447 3236848447</t>
-  </si>
-  <si>
-    <t>3236985225 3236985225</t>
-  </si>
-  <si>
-    <t>3237049086 3237049086</t>
-  </si>
-  <si>
-    <t>3237183195 3237183195</t>
+    <t>13:07</t>
+  </si>
+  <si>
+    <t>10:32</t>
+  </si>
+  <si>
+    <t>04:58</t>
+  </si>
+  <si>
+    <t>04:57</t>
+  </si>
+  <si>
+    <t>04:59</t>
+  </si>
+  <si>
+    <t>05:12</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ</t>
@@ -538,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -547,17 +523,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -597,104 +572,95 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46267</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46252</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>30</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.81</v>
+      </c>
+      <c r="H2" s="1">
+        <v>54.3</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="J2" s="1">
+        <v>55.2</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>13061</v>
+      </c>
+      <c r="M2">
+        <v>169772</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2">
-        <v>53</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>30</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.83</v>
+      </c>
+      <c r="H3" s="1">
+        <v>54.9</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.86</v>
+      </c>
+      <c r="J3" s="1">
+        <v>55.8</v>
+      </c>
+      <c r="K3" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="I2" s="1">
-        <v>93.81</v>
-      </c>
-      <c r="J2" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="K2" s="1">
-        <v>95.40000000000001</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2">
-        <v>159800</v>
-      </c>
-      <c r="N2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46252</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>45</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="I3" s="1">
-        <v>79.65000000000001</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="K3" s="1">
-        <v>81</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
+      <c r="L3">
+        <v>161430</v>
       </c>
       <c r="M3">
-        <v>12455</v>
-      </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>249683</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
-        <v>46258</v>
+        <v>46273</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
@@ -703,86 +669,80 @@
         <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>55</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.85</v>
       </c>
       <c r="H4" s="1">
-        <v>1.82</v>
+        <v>55.5</v>
       </c>
       <c r="I4" s="1">
-        <v>100.1</v>
+        <v>1.88</v>
       </c>
       <c r="J4" s="1">
-        <v>1.85</v>
-      </c>
-      <c r="K4" s="1">
-        <v>101.75</v>
-      </c>
-      <c r="L4" t="s">
-        <v>24</v>
+        <v>56.4</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4">
+        <v>161610</v>
       </c>
       <c r="M4">
-        <v>160290</v>
-      </c>
-      <c r="N4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>62611</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
-        <v>46261</v>
+        <v>46275</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
       <c r="F5">
-        <v>50</v>
-      </c>
-      <c r="G5" t="s">
-        <v>21</v>
+        <v>21.16</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.86</v>
       </c>
       <c r="H5" s="1">
-        <v>1.82</v>
+        <v>39.358</v>
       </c>
       <c r="I5" s="1">
-        <v>91</v>
+        <v>1.89</v>
       </c>
       <c r="J5" s="1">
-        <v>1.85</v>
-      </c>
-      <c r="K5" s="1">
-        <v>92.5</v>
-      </c>
-      <c r="L5" t="s">
-        <v>25</v>
+        <v>39.992</v>
+      </c>
+      <c r="K5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5">
+        <v>161825</v>
       </c>
       <c r="M5">
-        <v>12829</v>
-      </c>
-      <c r="N5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>62876</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
-        <v>46262</v>
+        <v>46275</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
         <v>16</v>
@@ -791,42 +751,39 @@
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>80</v>
-      </c>
-      <c r="G6" t="s">
-        <v>21</v>
+        <v>18.88</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.86</v>
       </c>
       <c r="H6" s="1">
-        <v>1.82</v>
+        <v>35.117</v>
       </c>
       <c r="I6" s="1">
-        <v>145.6</v>
+        <v>1.89</v>
       </c>
       <c r="J6" s="1">
-        <v>1.85</v>
-      </c>
-      <c r="K6" s="1">
-        <v>148</v>
-      </c>
-      <c r="L6" t="s">
-        <v>26</v>
+        <v>35.683</v>
+      </c>
+      <c r="K6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>161825</v>
       </c>
       <c r="M6">
-        <v>160810</v>
-      </c>
-      <c r="N6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>62877</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
-        <v>46265</v>
+        <v>46279</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
@@ -835,39 +792,36 @@
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>33</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
+        <v>49.99</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.89</v>
       </c>
       <c r="H7" s="1">
-        <v>1.81</v>
+        <v>94.48099999999999</v>
       </c>
       <c r="I7" s="1">
-        <v>59.73</v>
+        <v>1.92</v>
       </c>
       <c r="J7" s="1">
-        <v>1.84</v>
-      </c>
-      <c r="K7" s="1">
-        <v>60.72</v>
-      </c>
-      <c r="L7" t="s">
-        <v>27</v>
+        <v>95.98099999999999</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7">
+        <v>162030</v>
       </c>
       <c r="M7">
-        <v>160940</v>
-      </c>
-      <c r="N7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>63361</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -875,62 +829,62 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:13">
       <c r="A11" s="5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="7">
-        <v>316</v>
+        <v>180.03</v>
       </c>
       <c r="C12" s="8">
         <v>6</v>
       </c>
       <c r="D12" s="9">
-        <v>1.80345</v>
+        <v>1.85334</v>
       </c>
       <c r="E12" s="7">
-        <v>569.89</v>
+        <v>333.66</v>
       </c>
       <c r="F12" s="7">
-        <v>579.37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>339.06</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="10" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B13" s="11">
-        <v>316</v>
+        <v>180.03</v>
       </c>
       <c r="C13" s="12">
         <v>6</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="11">
-        <v>569.89</v>
+        <v>333.66</v>
       </c>
       <c r="F13" s="11">
-        <v>579.37</v>
+        <v>339.06</v>
       </c>
     </row>
   </sheetData>
